--- a/光伏配储项目/电价数据/2026/饶平站.xlsx
+++ b/光伏配储项目/电价数据/2026/饶平站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3378</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.77275</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07676999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.9763999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.01729</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17454</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25581</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26039</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8310700000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.50698</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60881</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59077</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75637</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.13769</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.72086</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67484</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.90461</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.4108</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.0838</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.09584</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3194</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40063</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72515</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7787999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.26825</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.81979</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.85454</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7923300000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.41521</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70841</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.6262</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8879199999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86095</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.49894</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49187</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47538</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49049</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.52558</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.67667</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6381100000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89009</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.11068</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.74303</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53422</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7062999999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.12066</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.66213</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.92772</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.06889</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.32253</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19517</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9687899999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.31585</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.17744</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.37495</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0658</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.16207</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7812899999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.99473</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03043</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9017200000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.12737</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.96474</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90008</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9106799999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50989</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.8974800000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7257</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.71293</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.91547</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.91213</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9341699999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.81643</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.82141</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.83299</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.04657</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5807599999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.64811</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9087999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.88927</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73913</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.79689</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5522100000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.95648</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.5392100000000001</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6460399999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.69421</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.67396</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.66096</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.63924</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.66375</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7010299999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51647</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.65907</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85824</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7946</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.06071</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47672</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.65534</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.48073</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5928600000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.72626</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.91074</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.63519</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09746</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.82175</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6363099999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5734400000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71227</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34158</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48178</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44158</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52215</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.74975</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45617</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.75498</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.60929</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.63385</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.8941399999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.64491</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6319400000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.65123</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8041900000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6618200000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.61717</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.58885</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37281</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14325</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25781</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10731</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03268</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31639</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18802</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.17954</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24614</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19166</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21192</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18952</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17051</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19776</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09637999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03965999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19417</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31529</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.42595</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44364</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48245</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78786</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87029</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65174</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5815399999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.62962</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.94041</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5405399999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43084</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.95829</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72953</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.57545</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17641</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27581</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32287</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.83311</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.21083</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.47563</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23278</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.18772</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.23813</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.25134</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.45459</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.44689</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.23821</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.48029</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.50749</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.54286</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29537</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.53304</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.69688</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.27286</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.11202</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23056</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46402</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.17173</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.50275</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31417</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19915</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.21355</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18402</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20851</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18128</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.22719</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18281</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20736</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.18267</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27977</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28592</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30282</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08032</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49782</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5537300000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.77534</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.57699</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.47051</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41586</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5415599999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.06182</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42642</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.20133</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.19774</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.16303</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.14163</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.27604</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19513</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18752</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27607</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18929</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18667</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14962</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26067</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19214</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.1987</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16236</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24573</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31994</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27278</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.59566</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5203</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29554</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49436</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.62549</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5869800000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.63313</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7785</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43656</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31314</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47772</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5172899999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5742999999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43429</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.93006</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6960499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.56488</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6417999999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31224</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.01187</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.51718</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.23397</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.30792</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.24764</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16208</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01339</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01592</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01532</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16233</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19625</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16112</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01561</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15194</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15636</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15406</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15936</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01599</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16201</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01609</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04187</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17265</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.15909</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21524</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.04771</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.21191</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.19849</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.21588</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.30629</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03307</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17782</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02742</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19753</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21913</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21057</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03954</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.02517</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02518</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02545</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02545</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02529</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19212</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03968</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02545</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02543</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17012</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03954999999999999</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03953</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02458</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02144</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.22636</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.005160000000000001</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02543</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03055</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.24386</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2659</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.009179999999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27242</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16151</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15685</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15476</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02131</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02018</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.01829</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18467</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85661</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8624299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08929999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02409</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47538</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6309400000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7511100000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.89737</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7658400000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.76407</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.76781</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8554299999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30488</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18257</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24319</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20986</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24735</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19604</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15952</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19173</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15422</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14845</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17377</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22512</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24374</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28862</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5558099999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45299</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46094</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7700900000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.77559</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52247</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65137</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81141</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19877</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31437</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48578</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.76525</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.52596</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6601699999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5385800000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6361100000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.59941</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.91847</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7799299999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.67725</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.56601</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31898</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26475</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.54318</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19843</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51136</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.47358</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.62599</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.60341</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.6595700000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5171699999999999</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.52471</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32281</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.67464</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.72273</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.74873</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.53344</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.62409</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.79871</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33693</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.59926</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17612</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14673</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04799</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22635</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14336</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18753</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.20653</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.23201</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.19614</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.68203</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.77677</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.54628</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.27027</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5958600000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6590900000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.73724</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6041599999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.7490599999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.10056</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.72758</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.43468</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.69539</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7249800000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.61538</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.45299</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3671</v>
       </c>
     </row>
   </sheetData>
